--- a/OCT_2026/10-09-26/Gourmet Food 1.xlsx
+++ b/OCT_2026/10-09-26/Gourmet Food 1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0A859B-27DA-4A49-8836-7EEAF63F18DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A580BB96-1C2C-4800-BAC3-3E00607E57B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="878" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2776,7 +2776,7 @@
     <xf numFmtId="43" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="416">
+  <cellXfs count="415">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3679,7 +3679,7 @@
     <xf numFmtId="0" fontId="41" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3963,9 +3963,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -7775,16 +7772,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -7796,19 +7791,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="96"/>
       <c r="S18" s="269">
@@ -7850,16 +7845,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -7871,19 +7864,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -7924,16 +7917,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>40</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -7945,24 +7936,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -8002,16 +7993,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -8023,19 +8012,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -8293,15 +8282,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>10815.300000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1946.7539999999995</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -8313,19 +8302,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>8868.5460000000003</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>2044.0677966101694</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>54.563068983050847</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>10967.176865593219</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -8379,7 +8368,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>10815.300000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8400,7 +8389,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1946.7539999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8443,7 +8432,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>8868.5460000000021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8467,7 +8456,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>2044.0677966101694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8489,7 +8478,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>10912.613796610171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8514,7 +8503,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>54.563068983050854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8524,7 +8513,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>10967.176865593221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9054,16 +9043,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
@@ -9075,19 +9062,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P16" s="309">
         <f>M16+N16+O16</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="312"/>
       <c r="S16" s="269">
@@ -9206,16 +9193,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -9227,19 +9212,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -9718,15 +9703,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>755.45999999999992</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -9738,19 +9723,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>3441.54</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>793.22033898305051</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>21.173801694915252</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>4255.9341406779649</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -9804,7 +9789,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>4197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9825,7 +9810,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>755.45999999999992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9868,7 +9853,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>3441.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9892,7 +9877,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>793.22033898305051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9914,7 +9899,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>4234.7603389830501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9939,7 +9924,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>21.173801694915252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9949,7 +9934,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>4255.9341406779649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10479,16 +10464,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
@@ -10500,21 +10483,23 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P16" s="309">
         <f>M16+N16+O16</f>
-        <v>2127.9670703389825</v>
-      </c>
-      <c r="Q16" s="312"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="312">
+        <v>40</v>
+      </c>
       <c r="S16" s="269">
         <v>0.18</v>
       </c>
@@ -10555,16 +10540,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>40</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -10576,21 +10559,23 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
-      </c>
-      <c r="Q17" s="156"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="156">
+        <v>40</v>
+      </c>
       <c r="S17" s="269">
         <f>+S16</f>
         <v>0.18</v>
@@ -10854,16 +10839,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -10875,21 +10858,23 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
-      </c>
-      <c r="Q21" s="156"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="156">
+        <v>40</v>
+      </c>
       <c r="S21" s="269">
         <f>+S20</f>
         <v>0.18</v>
@@ -11145,15 +11130,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>7102.6</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1278.4679999999998</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -11165,23 +11150,23 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>5824.1319999999996</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1342.3728813559319</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>35.832524406779655</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>7202.3374057627107</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
@@ -11231,7 +11216,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>7102.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11252,7 +11237,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1278.4679999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11295,7 +11280,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>5824.1320000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11319,7 +11304,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1342.3728813559319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11341,7 +11326,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>7166.5048813559324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11366,7 +11351,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>35.832524406779662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11376,7 +11361,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>7202.3374057627125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12129,16 +12114,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -12150,19 +12133,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -12279,16 +12262,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -12300,19 +12281,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -12570,15 +12551,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1046.0159999999998</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -12590,19 +12571,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>4765.1840000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1098.3050847457628</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>29.317445423728813</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>5892.8065301694915</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -12656,7 +12637,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12677,7 +12658,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1046.0159999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12720,7 +12701,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>4765.1840000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12744,7 +12725,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1098.3050847457628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12766,7 +12747,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>5863.4890847457627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -12791,7 +12772,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>29.317445423728813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -12801,7 +12782,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>5892.8065301694915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -13481,16 +13462,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -13502,19 +13481,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="96"/>
       <c r="S18" s="269">
@@ -13628,16 +13607,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>40</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -13649,24 +13626,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -13995,15 +13972,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>5004.1000000000004</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>900.73799999999983</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -14015,19 +13992,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>4103.3620000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>945.76271186440658</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>25.245623559322034</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>5074.3703354237277</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -14081,7 +14058,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>5004.1000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14102,7 +14079,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>900.73799999999983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14145,7 +14122,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>4103.362000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14169,7 +14146,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>945.76271186440658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -14191,7 +14168,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>5049.1247118644078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14216,7 +14193,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>25.245623559322041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -14226,7 +14203,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>5074.3703354237296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -19035,16 +19012,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
@@ -19056,21 +19031,23 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P16" s="309">
         <f>M16+N16+O16</f>
-        <v>2127.9670703389825</v>
-      </c>
-      <c r="Q16" s="312"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="312">
+        <v>40</v>
+      </c>
       <c r="S16" s="269">
         <v>0.18</v>
       </c>
@@ -19261,15 +19238,15 @@
       </c>
       <c r="G19" s="287"/>
       <c r="H19" s="96">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>1452.8</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>261.50399999999996</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -19281,21 +19258,23 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>1191.296</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>7.3293613559322033</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
-      </c>
-      <c r="Q19" s="156"/>
+        <v>1473.2016325423729</v>
+      </c>
+      <c r="Q19" s="156">
+        <v>20</v>
+      </c>
       <c r="S19" s="269">
         <f>+S18</f>
         <v>0.18</v>
@@ -19335,15 +19314,15 @@
       </c>
       <c r="G20" s="287"/>
       <c r="H20" s="96">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>1452.8</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>261.50399999999996</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -19355,24 +19334,26 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>1191.296</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>7.3293613559322033</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
-      </c>
-      <c r="Q20" s="156"/>
+        <v>1473.2016325423729</v>
+      </c>
+      <c r="Q20" s="156">
+        <v>20</v>
+      </c>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>70.152458692493951</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -19413,15 +19394,15 @@
       </c>
       <c r="G21" s="287"/>
       <c r="H21" s="96">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>1452.8</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>261.50399999999996</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -19433,21 +19414,23 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>1191.296</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>7.3293613559322033</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
-      </c>
-      <c r="Q21" s="96"/>
+        <v>1473.2016325423729</v>
+      </c>
+      <c r="Q21" s="96">
+        <v>20</v>
+      </c>
       <c r="S21" s="269">
         <f>+S20</f>
         <v>0.18</v>
@@ -19703,15 +19686,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>10815.300000000001</v>
+        <v>4358.3999999999996</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1946.7539999999995</v>
+        <v>784.51199999999994</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -19723,23 +19706,23 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>8868.5460000000003</v>
+        <v>3573.8879999999999</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>2044.0677966101694</v>
+        <v>823.72881355932213</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>54.563068983050847</v>
+        <v>21.98808406779661</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>10967.176865593219</v>
+        <v>4419.6048976271186</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
@@ -19789,7 +19772,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>10815.300000000001</v>
+        <v>4358.3999999999996</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19810,7 +19793,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1946.7539999999995</v>
+        <v>784.51199999999994</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19853,7 +19836,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>8868.5460000000021</v>
+        <v>3573.8879999999999</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19877,7 +19860,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>2044.0677966101694</v>
+        <v>823.72881355932213</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19899,7 +19882,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>10912.613796610171</v>
+        <v>4397.6168135593216</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19924,7 +19907,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>54.563068983050854</v>
+        <v>21.98808406779661</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -19934,7 +19917,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>10967.176865593221</v>
+        <v>4419.6048976271186</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -20464,16 +20447,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
@@ -20485,19 +20466,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P16" s="309">
         <f>M16+N16+O16</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="156"/>
       <c r="S16" s="269">
@@ -20540,16 +20521,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>40</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -20561,19 +20540,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="156"/>
       <c r="S17" s="269">
@@ -20618,16 +20597,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -20639,19 +20616,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -20693,16 +20670,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -20714,19 +20689,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -20767,16 +20742,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>40</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -20788,24 +20761,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -20845,16 +20818,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -20866,19 +20837,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -21136,15 +21107,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>15012.300000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>2702.2139999999995</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -21156,19 +21127,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>12310.086000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>2837.2881355932195</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>75.736870677966095</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>15223.111006271185</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -21222,7 +21193,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21243,7 +21214,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>2702.2139999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21286,7 +21257,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21310,7 +21281,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>2837.2881355932195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21332,7 +21303,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>15147.374135593222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -21357,7 +21328,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>75.73687067796611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -21367,7 +21338,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>15223.111006271187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24312,16 +24283,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
@@ -24333,19 +24302,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P16" s="309">
         <f>M16+N16+O16</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="312"/>
       <c r="S16" s="269">
@@ -24388,16 +24357,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="112">
-        <v>40</v>
-      </c>
+      <c r="H17" s="112"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -24409,19 +24376,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="156"/>
       <c r="S17" s="269">
@@ -24466,16 +24433,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="112">
-        <v>40</v>
-      </c>
+      <c r="H18" s="112"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -24487,19 +24452,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -24541,16 +24506,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="112">
-        <v>40</v>
-      </c>
+      <c r="H19" s="112"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -24562,19 +24525,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -24615,16 +24578,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="112">
-        <v>40</v>
-      </c>
+      <c r="H20" s="112"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -24636,24 +24597,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -24693,16 +24654,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="112">
-        <v>40</v>
-      </c>
+      <c r="H21" s="112"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -24714,19 +24673,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -24984,15 +24943,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>15012.300000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>2702.2139999999995</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -25004,19 +24963,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>12310.086000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>2837.2881355932195</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>75.736870677966095</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>15223.111006271185</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -25070,7 +25029,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25091,7 +25050,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>2702.2139999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25135,7 +25094,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25159,7 +25118,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>2837.2881355932195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25181,7 +25140,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>15147.374135593222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25206,7 +25165,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>75.73687067796611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25216,7 +25175,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>15223.111006271187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25746,16 +25705,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
@@ -25767,19 +25724,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P16" s="309">
         <f>M16+N16+O16</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="312"/>
       <c r="S16" s="269">
@@ -25898,16 +25855,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -25919,19 +25874,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -25973,16 +25928,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -25994,19 +25947,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -26047,16 +26000,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>40</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -26068,24 +26019,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -26125,16 +26076,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="304">
-        <v>40</v>
-      </c>
+      <c r="H21" s="304"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -26146,19 +26095,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -26416,15 +26365,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>12913.800000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>2324.4839999999995</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -26436,19 +26385,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>10589.316000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>2440.6779661016944</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>65.149969830508468</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>13095.143935932201</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -26502,7 +26451,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>12913.800000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26523,7 +26472,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>2324.4839999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26566,7 +26515,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>10589.316000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26590,7 +26539,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>2440.6779661016944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26612,7 +26561,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>13029.993966101698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26637,7 +26586,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>65.149969830508496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26647,7 +26596,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>13095.143935932207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27177,16 +27126,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
@@ -27198,19 +27145,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P16" s="309">
         <f>M16+N16+O16</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="312"/>
       <c r="S16" s="269">
@@ -27253,16 +27200,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="112">
-        <v>40</v>
-      </c>
+      <c r="H17" s="112"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -27274,19 +27219,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="96"/>
       <c r="S17" s="269">
@@ -27331,16 +27276,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="112">
-        <v>40</v>
-      </c>
+      <c r="H18" s="112"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -27352,19 +27295,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -27406,16 +27349,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="112">
-        <v>40</v>
-      </c>
+      <c r="H19" s="112"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -27427,19 +27368,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -27480,16 +27421,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="112">
-        <v>40</v>
-      </c>
+      <c r="H20" s="112"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -27501,24 +27440,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -27558,16 +27497,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="112">
-        <v>40</v>
-      </c>
+      <c r="H21" s="112"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -27579,19 +27516,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -27849,15 +27786,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>15012.300000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>2702.2139999999995</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -27869,19 +27806,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>12310.086000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>2837.2881355932195</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>75.736870677966095</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>15223.111006271185</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -27935,7 +27872,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27956,7 +27893,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>2702.2139999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27999,7 +27936,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>12310.086000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28023,7 +27960,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>2837.2881355932195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28045,7 +27982,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>15147.374135593222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28070,7 +28007,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>75.73687067796611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28080,7 +28017,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>15223.111006271187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30031,16 +29968,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
@@ -30052,19 +29987,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P16" s="309">
         <f>M16+N16+O16</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="312"/>
       <c r="S16" s="269">
@@ -30107,16 +30042,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>40</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -30128,19 +30061,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="156"/>
       <c r="S17" s="269">
@@ -30185,16 +30118,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -30206,19 +30137,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -30697,15 +30628,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>6295.5</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1133.1899999999998</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -30717,19 +30648,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>5162.3099999999995</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1189.8305084745757</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>31.760702542372876</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>6383.9012110169479</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -30783,7 +30714,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>6295.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30804,7 +30735,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1133.1899999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30847,7 +30778,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>5162.3100000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30871,7 +30802,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1189.8305084745757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30893,7 +30824,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>6352.1405084745766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30918,7 +30849,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>31.760702542372883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30928,7 +30859,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>6383.9012110169497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -31532,16 +31463,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>40</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -31553,19 +31482,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="156"/>
       <c r="S17" s="269">
@@ -31610,16 +31539,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -31631,19 +31558,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -31685,16 +31612,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -31706,19 +31631,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -31759,16 +31684,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>40</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -31780,24 +31703,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -32126,15 +32049,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>10008.200000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1801.4759999999997</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -32146,19 +32069,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>8206.7240000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1891.5254237288132</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>50.491247118644061</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>10148.740670847455</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -32212,7 +32135,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>10008.200000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32233,7 +32156,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1801.4759999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32276,7 +32199,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>8206.724000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32300,7 +32223,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1891.5254237288132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32322,7 +32245,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>10098.249423728816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32347,7 +32270,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>50.491247118644083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32357,7 +32280,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>10148.740670847459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -33110,16 +33033,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -33131,19 +33052,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -33260,16 +33181,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -33281,19 +33200,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -33551,15 +33470,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1046.0159999999998</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -33571,19 +33490,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>4765.1840000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1098.3050847457628</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>29.317445423728813</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>5892.8065301694915</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -33637,7 +33556,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33658,7 +33577,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1046.0159999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33701,7 +33620,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>4765.1840000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33725,7 +33644,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1098.3050847457628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33747,7 +33666,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>5863.4890847457627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -33772,7 +33691,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>29.317445423728813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -33782,7 +33701,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>5892.8065301694915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -34535,16 +34454,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -34556,19 +34473,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -34609,16 +34526,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>40</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -34630,24 +34545,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -34687,16 +34602,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -34708,19 +34621,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -34978,15 +34891,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>8716.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1569.0239999999999</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -34998,19 +34911,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>7147.7759999999998</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1647.4576271186443</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>43.97616813559322</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>8839.2097952542372</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -35064,7 +34977,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>8716.7999999999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35085,7 +34998,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1569.0239999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35128,7 +35041,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>7147.7759999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35152,7 +35065,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1647.4576271186443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35174,7 +35087,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>8795.2336271186432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -35199,7 +35112,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>43.97616813559322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -35209,7 +35122,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>8839.2097952542372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -35813,16 +35726,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>40</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -35834,19 +35745,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="156"/>
       <c r="S17" s="269">
@@ -36112,16 +36023,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -36133,19 +36042,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -36403,15 +36312,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>5004.1000000000004</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>900.73799999999983</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -36423,19 +36332,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>4103.3620000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>945.76271186440658</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>25.245623559322034</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>5074.3703354237277</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -36489,7 +36398,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>5004.1000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36510,7 +36419,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>900.73799999999983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36553,7 +36462,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>4103.362000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36577,7 +36486,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>945.76271186440658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36599,7 +36508,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>5049.1247118644078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -36624,7 +36533,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>25.245623559322041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -36634,7 +36543,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>5074.3703354237296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42929,16 +42838,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -42950,19 +42857,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -43152,16 +43059,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -43173,19 +43078,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -43443,15 +43348,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>5004.1000000000004</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>900.73799999999983</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -43463,19 +43368,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>4103.3620000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>945.76271186440658</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>25.245623559322034</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>5074.3703354237277</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -43529,7 +43434,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>5004.1000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43550,7 +43455,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>900.73799999999983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43593,7 +43498,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>4103.362000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43617,7 +43522,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>945.76271186440658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -43639,7 +43544,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>5049.1247118644078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -43664,7 +43569,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>25.245623559322041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -43674,7 +43579,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>5074.3703354237296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -48130,7 +48035,7 @@
       <c r="L4" s="371"/>
       <c r="M4" s="401">
         <f ca="1">TODAY()+1</f>
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="N4" s="401"/>
       <c r="O4" s="401"/>
@@ -48158,7 +48063,7 @@
       <c r="L5" s="371"/>
       <c r="M5" s="401">
         <f ca="1">M4-1</f>
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="N5" s="370"/>
       <c r="O5" s="370"/>
@@ -54376,7 +54281,7 @@
       </c>
       <c r="T3" s="300">
         <f>+'1'!P35</f>
-        <v>13095.143935932207</v>
+        <v>0</v>
       </c>
       <c r="XEW3" t="s">
         <v>80</v>
@@ -54398,7 +54303,7 @@
       </c>
       <c r="T4" s="300">
         <f>+'2'!P35</f>
-        <v>8020.7736005084762</v>
+        <v>0</v>
       </c>
       <c r="XEX4" t="s">
         <v>105</v>
@@ -54547,15 +54452,15 @@
       </c>
       <c r="H7" s="308">
         <f>+'1'!H16+'2'!H16+'3'!H16+'4'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16+'19'!H16+'20'!H16+'21'!H16+'22'!H16+'23'!H16+'24'!H16+'25'!H16+'26'!H16+'27'!H16+'28'!H16+'29'!H16+'30'!H16</f>
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="I7" s="235">
         <f>(G7*D7)*F7+H7*F7</f>
-        <v>25182</v>
+        <v>8394</v>
       </c>
       <c r="J7" s="286">
         <f>+'1'!J16+'2'!J16+'3'!J16+'4'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16+'19'!J16+'20'!J16+'21'!J16+'22'!J16+'23'!J16+'24'!J16+'25'!J16+'26'!J16+'27'!J16+'28'!J16+'29'!J16+'30'!J16</f>
-        <v>4532.7599999999993</v>
+        <v>1510.9199999999998</v>
       </c>
       <c r="K7" s="286">
         <f>+'1'!K16+'2'!K16+'3'!K16+'4'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16+'11'!K16+'12'!K16+'13'!K16+'14'!K16+'15'!K16+'16'!K16+'17'!K16+'18'!K16+'19'!K16+'20'!K16+'21'!K16+'22'!K16+'23'!K16+'24'!K16+'25'!K16+'26'!K16+'27'!K16+'28'!K16+'29'!K16+'30'!K16</f>
@@ -54567,23 +54472,23 @@
       </c>
       <c r="M7" s="229">
         <f>I7-SUM(J7:L7)</f>
-        <v>20649.240000000002</v>
+        <v>6883.08</v>
       </c>
       <c r="N7" s="286">
         <f>+'1'!N16+'2'!N16+'3'!N16+'4'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16+'11'!N16+'12'!N16+'13'!N16+'14'!N16+'15'!N16+'16'!N16+'17'!N16+'18'!N16+'19'!N16+'20'!N16+'21'!N16+'22'!N16+'23'!N16+'24'!N16+'25'!N16+'26'!N16+'27'!N16+'28'!N16+'29'!N16+'30'!N16</f>
-        <v>4759.3220338983019</v>
+        <v>1586.440677966101</v>
       </c>
       <c r="O7" s="286">
         <f>+'1'!O16+'2'!O16+'3'!O16+'4'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16+'11'!O16+'12'!O16+'13'!O16+'14'!O16+'15'!O16+'16'!O16+'17'!O16+'18'!O16+'19'!O16+'20'!O16+'21'!O16+'22'!O16+'23'!O16+'24'!O16+'25'!O16+'26'!O16+'27'!O16+'28'!O16+'29'!O16+'30'!O16</f>
-        <v>127.04281016949152</v>
+        <v>42.347603389830503</v>
       </c>
       <c r="P7" s="309">
         <f>M7+N7+O7</f>
-        <v>25535.604844067795</v>
+        <v>8511.8682813559299</v>
       </c>
       <c r="Q7" s="213">
         <f>+'1'!Q16+'2'!Q16+'3'!Q16+'4'!Q16+'5'!Q16+'6'!Q16+'7'!Q16+'8'!Q16+'9'!Q16+'10'!Q16+'11'!Q16+'12'!Q16+'13'!Q16+'14'!Q16+'15'!Q16+'16'!Q16+'17'!Q16+'18'!Q16+'19'!Q16+'20'!Q16+'21'!Q16+'22'!Q16+'23'!Q16+'24'!Q16+'25'!Q16+'26'!Q16+'27'!Q16+'28'!Q16+'29'!Q16+'30'!Q16</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R7" s="318">
         <v>5</v>
@@ -54630,15 +54535,15 @@
       </c>
       <c r="H8" s="308">
         <f>+'1'!H17+'2'!H17+'3'!H17+'4'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17+'17'!H17+'18'!H17+'19'!H17+'20'!H17+'21'!H17+'22'!H17+'23'!H17+'24'!H17+'25'!H17+'26'!H17+'27'!H17+'28'!H17+'29'!H17+'30'!H17</f>
-        <v>520</v>
+        <v>160</v>
       </c>
       <c r="I8" s="236">
         <f t="shared" ref="I8:I14" si="0">(G8*D8)*F8+H8*F8</f>
-        <v>27280.5</v>
+        <v>8394</v>
       </c>
       <c r="J8" s="286">
         <f>+'1'!J17+'2'!J17+'3'!J17+'4'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17+'19'!J17+'20'!J17+'21'!J17+'22'!J17+'23'!J17+'24'!J17+'25'!J17+'26'!J17+'27'!J17+'28'!J17+'29'!J17+'30'!J17</f>
-        <v>4910.4899999999989</v>
+        <v>1510.9199999999998</v>
       </c>
       <c r="K8" s="286">
         <f>+'1'!K17+'2'!K17+'3'!K17+'4'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17+'11'!K17+'12'!K17+'13'!K17+'14'!K17+'15'!K17+'16'!K17+'17'!K17+'18'!K17+'19'!K17+'20'!K17+'21'!K17+'22'!K17+'23'!K17+'24'!K17+'25'!K17+'26'!K17+'27'!K17+'28'!K17+'29'!K17+'30'!K17</f>
@@ -54650,23 +54555,23 @@
       </c>
       <c r="M8" s="230">
         <f t="shared" ref="M8:M15" si="1">I8-SUM(J8:L8)</f>
-        <v>22370.010000000002</v>
+        <v>6883.08</v>
       </c>
       <c r="N8" s="286">
         <f>+'1'!N17+'2'!N17+'3'!N17+'4'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17+'11'!N17+'12'!N17+'13'!N17+'14'!N17+'15'!N17+'16'!N17+'17'!N17+'18'!N17+'19'!N17+'20'!N17+'21'!N17+'22'!N17+'23'!N17+'24'!N17+'25'!N17+'26'!N17+'27'!N17+'28'!N17+'29'!N17+'30'!N17</f>
-        <v>5155.932203389827</v>
+        <v>1586.440677966101</v>
       </c>
       <c r="O8" s="286">
         <f>+'1'!O17+'2'!O17+'3'!O17+'4'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17+'11'!O17+'12'!O17+'13'!O17+'14'!O17+'15'!O17+'16'!O17+'17'!O17+'18'!O17+'19'!O17+'20'!O17+'21'!O17+'22'!O17+'23'!O17+'24'!O17+'25'!O17+'26'!O17+'27'!O17+'28'!O17+'29'!O17+'30'!O17</f>
-        <v>137.62971101694913</v>
+        <v>42.347603389830503</v>
       </c>
       <c r="P8" s="310">
         <f t="shared" ref="P8:P15" si="2">M8+N8+O8</f>
-        <v>27663.571914406781</v>
+        <v>8511.8682813559299</v>
       </c>
       <c r="Q8" s="213">
         <f>+'1'!Q17+'2'!Q17+'3'!Q17+'4'!Q17+'5'!Q17+'6'!Q17+'7'!Q17+'8'!Q17+'9'!Q17+'10'!Q17+'11'!Q17+'12'!Q17+'13'!Q17+'14'!Q17+'15'!Q17+'16'!Q17+'17'!Q17+'18'!Q17+'19'!Q17+'20'!Q17+'21'!Q17+'22'!Q17+'23'!Q17+'24'!Q17+'25'!Q17+'26'!Q17+'27'!Q17+'28'!Q17+'29'!Q17+'30'!Q17</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R8" s="318">
         <v>6</v>
@@ -54677,7 +54582,7 @@
       </c>
       <c r="T8" s="300">
         <f>+'6'!P35</f>
-        <v>10967.176865593221</v>
+        <v>0</v>
       </c>
       <c r="XEX8" t="s">
         <v>108</v>
@@ -54713,15 +54618,15 @@
       </c>
       <c r="H9" s="308">
         <f>+'1'!H18+'2'!H18+'3'!H18+'4'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18+'19'!H18+'20'!H18+'21'!H18+'22'!H18+'23'!H18+'24'!H18+'25'!H18+'26'!H18+'27'!H18+'28'!H18+'29'!H18+'30'!H18</f>
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="I9" s="236">
         <f t="shared" si="0"/>
-        <v>23083.5</v>
+        <v>0</v>
       </c>
       <c r="J9" s="286">
         <f>+'1'!J18+'2'!J18+'3'!J18+'4'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18+'19'!J18+'20'!J18+'21'!J18+'22'!J18+'23'!J18+'24'!J18+'25'!J18+'26'!J18+'27'!J18+'28'!J18+'29'!J18+'30'!J18</f>
-        <v>4155.03</v>
+        <v>0</v>
       </c>
       <c r="K9" s="286">
         <f>+'1'!K18+'2'!K18+'3'!K18+'4'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18+'11'!K18+'12'!K18+'13'!K18+'14'!K18+'15'!K18+'16'!K18+'17'!K18+'18'!K18+'19'!K18+'20'!K18+'21'!K18+'22'!K18+'23'!K18+'24'!K18+'25'!K18+'26'!K18+'27'!K18+'28'!K18+'29'!K18+'30'!K18</f>
@@ -54733,19 +54638,19 @@
       </c>
       <c r="M9" s="230">
         <f t="shared" si="1"/>
-        <v>18928.47</v>
+        <v>0</v>
       </c>
       <c r="N9" s="286">
         <f>+'1'!N18+'2'!N18+'3'!N18+'4'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18+'11'!N18+'12'!N18+'13'!N18+'14'!N18+'15'!N18+'16'!N18+'17'!N18+'18'!N18+'19'!N18+'20'!N18+'21'!N18+'22'!N18+'23'!N18+'24'!N18+'25'!N18+'26'!N18+'27'!N18+'28'!N18+'29'!N18+'30'!N18</f>
-        <v>4362.7118644067768</v>
+        <v>0</v>
       </c>
       <c r="O9" s="286">
         <f>+'1'!O18+'2'!O18+'3'!O18+'4'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18+'11'!O18+'12'!O18+'13'!O18+'14'!O18+'15'!O18+'16'!O18+'17'!O18+'18'!O18+'19'!O18+'20'!O18+'21'!O18+'22'!O18+'23'!O18+'24'!O18+'25'!O18+'26'!O18+'27'!O18+'28'!O18+'29'!O18+'30'!O18</f>
-        <v>116.45590932203389</v>
+        <v>0</v>
       </c>
       <c r="P9" s="310">
         <f t="shared" si="2"/>
-        <v>23407.637773728813</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="213">
         <f>+'1'!Q18+'2'!Q18+'3'!Q18+'4'!Q18+'5'!Q18+'6'!Q18+'7'!Q18+'8'!Q18+'9'!Q18+'10'!Q18+'11'!Q18+'12'!Q18+'13'!Q18+'14'!Q18+'15'!Q18+'16'!Q18+'17'!Q18+'18'!Q18+'19'!Q18+'20'!Q18+'21'!Q18+'22'!Q18+'23'!Q18+'24'!Q18+'25'!Q18+'26'!Q18+'27'!Q18+'28'!Q18+'29'!Q18+'30'!Q18</f>
@@ -54760,7 +54665,7 @@
       </c>
       <c r="T9" s="300">
         <f>+'7'!P35</f>
-        <v>4255.9341406779649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -54793,15 +54698,15 @@
       </c>
       <c r="H10" s="308">
         <f>+'1'!H19+'2'!H19+'3'!H19+'4'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19+'19'!H19+'20'!H19+'21'!H19+'22'!H19+'23'!H19+'24'!H19+'25'!H19+'26'!H19+'27'!H19+'28'!H19+'29'!H19+'30'!H19</f>
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="I10" s="236">
         <f t="shared" si="0"/>
-        <v>43584</v>
+        <v>10169.6</v>
       </c>
       <c r="J10" s="286">
         <f>+'1'!J19+'2'!J19+'3'!J19+'4'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19+'19'!J19+'20'!J19+'21'!J19+'22'!J19+'23'!J19+'24'!J19+'25'!J19+'26'!J19+'27'!J19+'28'!J19+'29'!J19+'30'!J19</f>
-        <v>7845.1199999999981</v>
+        <v>1830.5279999999998</v>
       </c>
       <c r="K10" s="286">
         <f>+'1'!K19+'2'!K19+'3'!K19+'4'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19+'11'!K19+'12'!K19+'13'!K19+'14'!K19+'15'!K19+'16'!K19+'17'!K19+'18'!K19+'19'!K19+'20'!K19+'21'!K19+'22'!K19+'23'!K19+'24'!K19+'25'!K19+'26'!K19+'27'!K19+'28'!K19+'29'!K19+'30'!K19</f>
@@ -54813,23 +54718,23 @@
       </c>
       <c r="M10" s="230">
         <f t="shared" si="1"/>
-        <v>35738.880000000005</v>
+        <v>8339.0720000000001</v>
       </c>
       <c r="N10" s="286">
         <f>+'1'!N19+'2'!N19+'3'!N19+'4'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19+'11'!N19+'12'!N19+'13'!N19+'14'!N19+'15'!N19+'16'!N19+'17'!N19+'18'!N19+'19'!N19+'20'!N19+'21'!N19+'22'!N19+'23'!N19+'24'!N19+'25'!N19+'26'!N19+'27'!N19+'28'!N19+'29'!N19+'30'!N19</f>
-        <v>8237.2881355932223</v>
+        <v>1922.0338983050847</v>
       </c>
       <c r="O10" s="286">
         <f>+'1'!O19+'2'!O19+'3'!O19+'4'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19+'11'!O19+'12'!O19+'13'!O19+'14'!O19+'15'!O19+'16'!O19+'17'!O19+'18'!O19+'19'!O19+'20'!O19+'21'!O19+'22'!O19+'23'!O19+'24'!O19+'25'!O19+'26'!O19+'27'!O19+'28'!O19+'29'!O19+'30'!O19</f>
-        <v>219.88084067796618</v>
+        <v>51.305529491525427</v>
       </c>
       <c r="P10" s="310">
         <f t="shared" si="2"/>
-        <v>44196.048976271188</v>
+        <v>10312.411427796609</v>
       </c>
       <c r="Q10" s="213">
         <f>+'1'!Q19+'2'!Q19+'3'!Q19+'4'!Q19+'5'!Q19+'6'!Q19+'7'!Q19+'8'!Q19+'9'!Q19+'10'!Q19+'11'!Q19+'12'!Q19+'13'!Q19+'14'!Q19+'15'!Q19+'16'!Q19+'17'!Q19+'18'!Q19+'19'!Q19+'20'!Q19+'21'!Q19+'22'!Q19+'23'!Q19+'24'!Q19+'25'!Q19+'26'!Q19+'27'!Q19+'28'!Q19+'29'!Q19+'30'!Q19</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R10" s="318">
         <v>8</v>
@@ -54840,7 +54745,7 @@
       </c>
       <c r="T10" s="300">
         <f>+'8'!P35</f>
-        <v>7202.3374057627125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -54873,15 +54778,15 @@
       </c>
       <c r="H11" s="308">
         <f>+'1'!H20+'2'!H20+'3'!H20+'4'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20+'19'!H20+'20'!H20+'21'!H20+'22'!H20+'23'!H20+'24'!H20+'25'!H20+'26'!H20+'27'!H20+'28'!H20+'29'!H20+'30'!H20</f>
-        <v>560</v>
+        <v>180</v>
       </c>
       <c r="I11" s="236">
         <f t="shared" si="0"/>
-        <v>40678.400000000001</v>
+        <v>13075.2</v>
       </c>
       <c r="J11" s="286">
         <f>+'1'!J20+'2'!J20+'3'!J20+'4'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20+'19'!J20+'20'!J20+'21'!J20+'22'!J20+'23'!J20+'24'!J20+'25'!J20+'26'!J20+'27'!J20+'28'!J20+'29'!J20+'30'!J20</f>
-        <v>7322.1119999999983</v>
+        <v>2353.5359999999996</v>
       </c>
       <c r="K11" s="286">
         <f>+'1'!K20+'2'!K20+'3'!K20+'4'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20+'11'!K20+'12'!K20+'13'!K20+'14'!K20+'15'!K20+'16'!K20+'17'!K20+'18'!K20+'19'!K20+'20'!K20+'21'!K20+'22'!K20+'23'!K20+'24'!K20+'25'!K20+'26'!K20+'27'!K20+'28'!K20+'29'!K20+'30'!K20</f>
@@ -54893,23 +54798,23 @@
       </c>
       <c r="M11" s="230">
         <f t="shared" si="1"/>
-        <v>33356.288</v>
+        <v>10721.664000000001</v>
       </c>
       <c r="N11" s="286">
         <f>+'1'!N20+'2'!N20+'3'!N20+'4'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20+'11'!N20+'12'!N20+'13'!N20+'14'!N20+'15'!N20+'16'!N20+'17'!N20+'18'!N20+'19'!N20+'20'!N20+'21'!N20+'22'!N20+'23'!N20+'24'!N20+'25'!N20+'26'!N20+'27'!N20+'28'!N20+'29'!N20+'30'!N20</f>
-        <v>7688.1355932203414</v>
+        <v>2471.1864406779659</v>
       </c>
       <c r="O11" s="286">
         <f>+'1'!O20+'2'!O20+'3'!O20+'4'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20+'11'!O20+'12'!O20+'13'!O20+'14'!O20+'15'!O20+'16'!O20+'17'!O20+'18'!O20+'19'!O20+'20'!O20+'21'!O20+'22'!O20+'23'!O20+'24'!O20+'25'!O20+'26'!O20+'27'!O20+'28'!O20+'29'!O20+'30'!O20</f>
-        <v>205.22211796610176</v>
+        <v>65.964252203389833</v>
       </c>
       <c r="P11" s="310">
         <f t="shared" si="2"/>
-        <v>41249.645711186444</v>
+        <v>13258.814692881357</v>
       </c>
       <c r="Q11" s="213">
         <f>+'1'!Q20+'2'!Q20+'3'!Q20+'4'!Q20+'5'!Q20+'6'!Q20+'7'!Q20+'8'!Q20+'9'!Q20+'10'!Q20+'11'!Q20+'12'!Q20+'13'!Q20+'14'!Q20+'15'!Q20+'16'!Q20+'17'!Q20+'18'!Q20+'19'!Q20+'20'!Q20+'21'!Q20+'22'!Q20+'23'!Q20+'24'!Q20+'25'!Q20+'26'!Q20+'27'!Q20+'28'!Q20+'29'!Q20+'30'!Q20</f>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R11" s="318">
         <v>9</v>
@@ -54920,7 +54825,7 @@
       </c>
       <c r="T11" s="300">
         <f>+'9'!P35</f>
-        <v>5892.8065301694915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -54953,15 +54858,15 @@
       </c>
       <c r="H12" s="308">
         <f>+'1'!H21+'2'!H21+'3'!H21+'4'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21+'19'!H21+'20'!H21+'21'!H21+'22'!H21+'23'!H21+'24'!H21+'25'!H21+'26'!H21+'27'!H21+'28'!H21+'29'!H21+'30'!H21</f>
-        <v>800</v>
+        <v>260</v>
       </c>
       <c r="I12" s="236">
         <f t="shared" si="0"/>
-        <v>58112</v>
+        <v>18886.400000000001</v>
       </c>
       <c r="J12" s="286">
         <f>+'1'!J21+'2'!J21+'3'!J21+'4'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21+'21'!J21+'22'!J21+'23'!J21+'24'!J21+'25'!J21+'26'!J21+'27'!J21+'28'!J21+'29'!J21+'30'!J21</f>
-        <v>10460.159999999998</v>
+        <v>3399.5519999999992</v>
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
@@ -54973,23 +54878,23 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>47651.840000000004</v>
+        <v>15486.848000000002</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
-        <v>10983.050847457631</v>
+        <v>3569.4915254237289</v>
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>293.17445423728822</v>
+        <v>95.28169762711866</v>
       </c>
       <c r="P12" s="310">
         <f t="shared" si="2"/>
-        <v>58928.065301694922</v>
+        <v>19151.621223050846</v>
       </c>
       <c r="Q12" s="213">
         <f>+'1'!Q21+'2'!Q21+'3'!Q21+'4'!Q21+'5'!Q21+'6'!Q21+'7'!Q21+'8'!Q21+'9'!Q21+'10'!Q21+'11'!Q21+'12'!Q21+'13'!Q21+'14'!Q21+'15'!Q21+'16'!Q21+'17'!Q21+'18'!Q21+'19'!Q21+'20'!Q21+'21'!Q21+'22'!Q21+'23'!Q21+'24'!Q21+'25'!Q21+'26'!Q21+'27'!Q21+'28'!Q21+'29'!Q21+'30'!Q21</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="R12" s="318">
         <v>10</v>
@@ -55000,7 +54905,7 @@
       </c>
       <c r="T12" s="300">
         <f>+'10'!P35</f>
-        <v>5074.3703354237296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55257,19 +55162,19 @@
       <c r="F16" s="374"/>
       <c r="G16" s="274">
         <f>H16/40</f>
-        <v>85</v>
+        <v>22.5</v>
       </c>
       <c r="H16" s="113">
         <f t="shared" ref="H16:M16" si="3">SUM(H7:H15)</f>
-        <v>3400</v>
+        <v>900</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="3"/>
-        <v>217920.4</v>
+        <v>58919.200000000004</v>
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>39225.671999999991</v>
+        <v>10605.455999999998</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
@@ -55281,23 +55186,23 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>178694.728</v>
+        <v>48313.744000000006</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
-        <v>41186.4406779661</v>
+        <v>11135.593220338982</v>
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>1099.4058433898308</v>
+        <v>297.24668610169493</v>
       </c>
       <c r="P16" s="113">
         <f>SUM(P7:P15)</f>
-        <v>220980.57452135591</v>
+        <v>59746.583906440675</v>
       </c>
       <c r="Q16" s="128">
         <f>SUM(Q7:Q15)</f>
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="R16" s="318">
         <v>14</v>
@@ -55308,7 +55213,7 @@
       </c>
       <c r="T16" s="300">
         <f>+'14'!P35</f>
-        <v>10967.176865593221</v>
+        <v>4419.6048976271186</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55336,7 +55241,7 @@
       </c>
       <c r="T17" s="300">
         <f>+'15'!P35</f>
-        <v>15223.111006271187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55357,7 +55262,7 @@
       </c>
       <c r="T18" s="300">
         <f>+'16'!P35</f>
-        <v>15223.111006271187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55380,7 +55285,7 @@
       <c r="O19" s="385"/>
       <c r="P19" s="139">
         <f>I16</f>
-        <v>217920.4</v>
+        <v>58919.200000000004</v>
       </c>
       <c r="R19" s="299">
         <v>17</v>
@@ -55391,7 +55296,7 @@
       </c>
       <c r="T19" s="300">
         <f>+'17'!P35</f>
-        <v>13095.143935932207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55412,7 +55317,7 @@
       <c r="O20" s="387"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>39225.671999999991</v>
+        <v>10605.455999999998</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -55423,7 +55328,7 @@
       </c>
       <c r="T20" s="300">
         <f>+'18'!P35</f>
-        <v>15223.111006271187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55477,7 +55382,7 @@
       <c r="O22" s="387"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>178694.728</v>
+        <v>48313.744000000006</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -55488,7 +55393,7 @@
       </c>
       <c r="T22" s="300">
         <f>+'20'!P35</f>
-        <v>6383.9012110169497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55512,7 +55417,7 @@
       </c>
       <c r="P23" s="140">
         <f>+N16</f>
-        <v>41186.4406779661</v>
+        <v>11135.593220338982</v>
       </c>
       <c r="R23" s="299">
         <v>21</v>
@@ -55523,7 +55428,7 @@
       </c>
       <c r="T23" s="300">
         <f>+'21'!P35</f>
-        <v>10148.740670847459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -55545,7 +55450,7 @@
       <c r="O24" s="389"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>219881.16867796611</v>
+        <v>59449.337220338988</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -55556,7 +55461,7 @@
       </c>
       <c r="T24" s="300">
         <f>+'22'!P35</f>
-        <v>5892.8065301694915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55581,7 +55486,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>1099.4058433898308</v>
+        <v>297.24668610169493</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -55592,7 +55497,7 @@
       </c>
       <c r="T25" s="300">
         <f>+'23'!P35</f>
-        <v>8839.2097952542372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55602,7 +55507,7 @@
       <c r="O26" s="346"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>220980.57452135594</v>
+        <v>59746.583906440683</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -55613,7 +55518,7 @@
       </c>
       <c r="T26" s="300">
         <f>+'24'!P35</f>
-        <v>5074.3703354237296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -55667,14 +55572,14 @@
       </c>
       <c r="T29" s="300">
         <f>+'27'!P35</f>
-        <v>5074.3703354237296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="R30" s="299">
         <v>28</v>
       </c>
-      <c r="S30" s="415" t="str">
+      <c r="S30" s="320" t="str">
         <f>+'28'!A6:A6</f>
         <v>Gourmet Food Riwind Road</v>
       </c>
@@ -55687,7 +55592,7 @@
       <c r="R31" s="299">
         <v>29</v>
       </c>
-      <c r="S31" s="415" t="str">
+      <c r="S31" s="320" t="str">
         <f>+'29'!A6:A6</f>
         <v xml:space="preserve">Gourmet Food  Chung </v>
       </c>
@@ -55700,7 +55605,7 @@
       <c r="R32" s="299">
         <v>30</v>
       </c>
-      <c r="S32" s="415" t="str">
+      <c r="S32" s="320" t="str">
         <f>+'30'!A6:A6</f>
         <v>Gourmet Food Moter Way</v>
       </c>
@@ -55716,7 +55621,7 @@
       </c>
       <c r="T33" s="303">
         <f>SUM(T3:T32)</f>
-        <v>220980.57452135594</v>
+        <v>59746.58390644069</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -56297,16 +56202,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>40</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -56318,19 +56221,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="156"/>
       <c r="S17" s="269">
@@ -56375,16 +56278,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" ref="I18:I21" si="7">(G18*D18)*F18+H18*F18</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
@@ -56396,19 +56297,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P18" s="310">
         <f t="shared" si="5"/>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="96"/>
       <c r="S18" s="269">
@@ -56450,16 +56351,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="7"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -56471,19 +56370,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -56524,16 +56423,14 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>40</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="7"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
@@ -56545,24 +56442,24 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P20" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>140.3049173849879</v>
+        <v>0</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
@@ -56602,16 +56499,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="7"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -56623,19 +56518,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -56893,15 +56788,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" ref="H25" si="9">SUM(H16:H24)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" ref="I25:M25" si="10">SUM(I16:I24)</f>
-        <v>12913.800000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>2324.4839999999995</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="10"/>
@@ -56913,19 +56808,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="10"/>
-        <v>10589.316000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>2440.6779661016944</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>65.149969830508468</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>13095.143935932201</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -56979,7 +56874,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>12913.800000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57000,7 +56895,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>2324.4839999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57043,7 +56938,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>10589.316000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57067,7 +56962,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>2440.6779661016944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57089,7 +56984,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>13029.993966101698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -57114,7 +57009,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>65.149969830508496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -57124,7 +57019,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>13095.143935932207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -57720,16 +57615,14 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>40</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>377.72999999999996</v>
+        <v>0</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
@@ -57741,19 +57634,19 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>1720.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>10.586900847457626</v>
+        <v>0</v>
       </c>
       <c r="P17" s="310">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>2127.9670703389825</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="156"/>
       <c r="S17" s="269">
@@ -57871,16 +57764,14 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -57892,19 +57783,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P19" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -58021,16 +57912,14 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>40</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>523.00799999999992</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -58042,19 +57931,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2382.5920000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>14.658722711864407</v>
+        <v>0</v>
       </c>
       <c r="P21" s="310">
         <f t="shared" si="5"/>
-        <v>2946.4032650847457</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -58312,15 +58201,15 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>7909.7000000000007</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1423.7459999999996</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -58332,19 +58221,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>6485.9539999999997</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1494.9152542372881</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>39.904346271186441</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>8020.7736005084735</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
@@ -58398,7 +58287,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>7909.7000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58419,7 +58308,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1423.7459999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58462,7 +58351,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>6485.9540000000015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58486,7 +58375,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1494.9152542372881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58508,7 +58397,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>7980.8692542372901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -58533,7 +58422,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>39.904346271186448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -58543,7 +58432,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>8020.7736005084762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -59401,9 +59290,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="156">
-        <v>40</v>
-      </c>
+      <c r="Q20" s="156"/>
       <c r="R20">
         <f>P20/21</f>
         <v>0</v>
@@ -59479,9 +59366,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="156">
-        <v>40</v>
-      </c>
+      <c r="Q21" s="156"/>
       <c r="S21" s="269">
         <f>+S20</f>
         <v>0.18</v>
@@ -59773,7 +59658,7 @@
       </c>
       <c r="Q25" s="128">
         <f>SUM(Q16:Q24)</f>
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
